--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B91A4D4-8740-41E5-8262-CF344CF5DC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DF0C14-87A8-4E05-A0F8-25E03159F700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21660" yWindow="-13800" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Temps</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Création de la solution + projet maui pour le design</t>
+  </si>
+  <si>
+    <t>UI + Wizard + Create Competition Step</t>
   </si>
 </sst>
 </file>
@@ -192,8 +195,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E5" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E7" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E6" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -489,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -621,20 +624,39 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>200</v>
-      </c>
-      <c r="E6">
+        <v>290</v>
+      </c>
+      <c r="E7">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DF0C14-87A8-4E05-A0F8-25E03159F700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4737C04E-3459-4BD8-AB07-679655253196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21660" yWindow="-13800" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Temps</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>UI + Wizard + Create Competition Step</t>
+  </si>
+  <si>
+    <t>Architecture</t>
   </si>
 </sst>
 </file>
@@ -195,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E7" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E6" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E8" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E7" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -492,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -643,20 +646,39 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3">
+        <v>46083</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>9</v>
-      </c>
-      <c r="D7" s="2">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>290</v>
-      </c>
-      <c r="E7">
+        <v>350</v>
+      </c>
+      <c r="E8">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4737C04E-3459-4BD8-AB07-679655253196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98ED9D3-7BA8-442B-AD30-EC3B385E814C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21660" yWindow="-13800" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Temps</t>
   </si>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E8" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E7" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E9" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E8" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -665,20 +665,39 @@
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>11</v>
-      </c>
-      <c r="D8" s="2">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>350</v>
-      </c>
-      <c r="E8">
+        <v>380</v>
+      </c>
+      <c r="E9">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98ED9D3-7BA8-442B-AD30-EC3B385E814C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C366CF94-89C2-4BB6-9F12-241B5C529FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21660" yWindow="-13800" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Temps</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Architecture</t>
+  </si>
+  <si>
+    <t>Architecture + controles (button, theme, etc…)</t>
   </si>
 </sst>
 </file>
@@ -669,17 +672,17 @@
         <v>46084</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2">
         <v>30</v>
       </c>
       <c r="D8" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2"/>
     </row>
@@ -689,11 +692,11 @@
       </c>
       <c r="B9" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="E9">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C366CF94-89C2-4BB6-9F12-241B5C529FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C993DBD-5591-4CC7-BCE0-1B408951E1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21660" yWindow="-13800" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15300" yWindow="-15360" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Temps</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Architecture + controles (button, theme, etc…)</t>
+  </si>
+  <si>
+    <t>Controls UI + Wizard</t>
   </si>
 </sst>
 </file>
@@ -201,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E9" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E8" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E10" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E9" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -687,20 +690,39 @@
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>13</v>
-      </c>
-      <c r="D9" s="2">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>410</v>
-      </c>
-      <c r="E9">
+        <v>470</v>
+      </c>
+      <c r="E10">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C993DBD-5591-4CC7-BCE0-1B408951E1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35ED34B-BB0A-486A-AAA6-3EC1814A07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15300" yWindow="-15360" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,14 +694,14 @@
         <v>46086</v>
       </c>
       <c r="B9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2">
         <v>30</v>
       </c>
       <c r="D9" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -714,11 +714,11 @@
       </c>
       <c r="B10" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="E10">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35ED34B-BB0A-486A-AAA6-3EC1814A07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F7F64-D6B0-4775-A815-24BB8E65A90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15300" yWindow="-15360" windowWidth="28800" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -204,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E10" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E9" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E11" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E10" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -501,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -694,14 +695,14 @@
         <v>46086</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
         <v>30</v>
       </c>
       <c r="D9" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -709,18 +710,34 @@
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3">
+        <v>46088</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>35</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>16</v>
-      </c>
-      <c r="D10" s="2">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>500</v>
-      </c>
-      <c r="E10">
+        <v>595</v>
+      </c>
+      <c r="E11">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>8</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F7F64-D6B0-4775-A815-24BB8E65A90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754E56D4-66CF-42D7-8327-235E4048AD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -714,14 +714,14 @@
         <v>46088</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2">
         <v>35</v>
       </c>
       <c r="D10" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -731,11 +731,11 @@
       </c>
       <c r="B11" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>595</v>
+        <v>630</v>
       </c>
       <c r="E11">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754E56D4-66CF-42D7-8327-235E4048AD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E25269-61DB-4287-B5A9-614B4C30A41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Temps</t>
   </si>
@@ -91,6 +90,9 @@
   </si>
   <si>
     <t>Controls UI + Wizard</t>
+  </si>
+  <si>
+    <t>Formulaire</t>
   </si>
 </sst>
 </file>
@@ -205,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E11" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E10" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E13" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E12" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -502,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -726,20 +728,55 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46093</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B13" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>20</v>
-      </c>
-      <c r="D11" s="2">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>630</v>
-      </c>
-      <c r="E11">
+        <v>750</v>
+      </c>
+      <c r="E13">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E25269-61DB-4287-B5A9-614B4C30A41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789D70D-720C-489E-86F1-CE22E5F11C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E13" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E12" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E14" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E13" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -763,18 +763,34 @@
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3">
+        <v>46097</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B14" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>24</v>
-      </c>
-      <c r="D13" s="2">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>750</v>
-      </c>
-      <c r="E13">
+        <v>810</v>
+      </c>
+      <c r="E14">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789D70D-720C-489E-86F1-CE22E5F11C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7615E61-AC8F-4DCE-8103-10066E2EB3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E14" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E13" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E15" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E14" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -767,30 +767,46 @@
         <v>46097</v>
       </c>
       <c r="B13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2">
         <v>30</v>
       </c>
       <c r="D13" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B15" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
         <v>26</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D15" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
         <v>810</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7615E61-AC8F-4DCE-8103-10066E2EB3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED6415D-1DD0-44FF-89CD-C111BBDEA876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E15" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E14" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E18" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E17" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -586,11 +586,11 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -605,11 +605,11 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -767,14 +767,14 @@
         <v>46097</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>30</v>
       </c>
       <c r="D13" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -783,30 +783,78 @@
         <v>46098</v>
       </c>
       <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>45734</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>45735</v>
+      </c>
+      <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
-        <v>30</v>
-      </c>
-      <c r="D14" s="2">
-        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="C16" s="2">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>45739</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B18" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>26</v>
-      </c>
-      <c r="D15" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>810</v>
-      </c>
-      <c r="E15">
+        <v>970</v>
+      </c>
+      <c r="E18">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED6415D-1DD0-44FF-89CD-C111BBDEA876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E8D51F-4C64-4D9B-A4CE-B1992E83912E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E18" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E17" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E19" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E18" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -843,18 +843,34 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3">
+        <v>45740</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B19" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>32</v>
-      </c>
-      <c r="D18" s="2">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>970</v>
-      </c>
-      <c r="E18">
+        <v>1000</v>
+      </c>
+      <c r="E19">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E8D51F-4C64-4D9B-A4CE-B1992E83912E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ACDEA7-BC49-4A3F-B773-4B9687491833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -99,8 +99,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -131,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -151,6 +152,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,6 +171,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
@@ -182,9 +187,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -207,15 +209,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E19" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E18" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E20" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E19" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{F6272052-D21F-4D8F-847C-BBBD7A5BFBB5}" name="Taux (horaire)" dataDxfId="8" totalsRowDxfId="1">
+    <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F6272052-D21F-4D8F-847C-BBBD7A5BFBB5}" name="Taux (horaire)" dataDxfId="9" totalsRowDxfId="1">
       <calculatedColumnFormula>Tableau2[[#This Row],[Prix horaire]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0D374421-71FB-4B26-A655-B8932AB5024B}" name="Prix" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{0D374421-71FB-4B26-A655-B8932AB5024B}" name="Prix" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="0">
       <calculatedColumnFormula>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{AFE2A571-8D78-4F39-B21A-AD4ADB93030D}" name="Détails" totalsRowFunction="count"/>
@@ -228,11 +230,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9E2C1EA8-ABF8-4B8F-A346-A6735D728120}" name="Tableau2" displayName="Tableau2" ref="G1:J2" totalsRowShown="0">
   <autoFilter ref="G1:J2" xr:uid="{9E2C1EA8-ABF8-4B8F-A346-A6735D728120}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{66CCC7CF-8A36-43CE-820F-0890999AEE46}" name="Salaire" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AD6BD5F4-3FC8-4450-A6E7-FDD7C0FEA506}" name="Horaire" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{66CCC7CF-8A36-43CE-820F-0890999AEE46}" name="Salaire" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{AD6BD5F4-3FC8-4450-A6E7-FDD7C0FEA506}" name="Horaire" dataDxfId="6">
       <calculatedColumnFormula>35*4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F29CA281-385D-4D4D-97E5-98E515379F73}" name="Heure / jour" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F29CA281-385D-4D4D-97E5-98E515379F73}" name="Heure / jour" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{6CCB0674-3E10-4292-8D20-2B8C7040EA90}" name="Prix horaire">
       <calculatedColumnFormula>Tableau2[[#This Row],[Salaire]]/Tableau2[[#This Row],[Horaire]]</calculatedColumnFormula>
     </tableColumn>
@@ -504,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -550,7 +552,7 @@
       <c r="A2" s="3">
         <v>46052</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="9">
         <v>1</v>
       </c>
       <c r="C2" s="2">
@@ -582,7 +584,7 @@
       <c r="A3" s="3">
         <v>46053</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
       <c r="C3" s="2">
@@ -601,7 +603,7 @@
       <c r="A4" s="3">
         <v>46053</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="9">
         <v>3</v>
       </c>
       <c r="C4" s="2">
@@ -620,7 +622,7 @@
       <c r="A5" s="3">
         <v>46077</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="9">
         <v>1</v>
       </c>
       <c r="C5" s="2">
@@ -639,7 +641,7 @@
       <c r="A6" s="3">
         <v>46080</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="9">
         <v>3</v>
       </c>
       <c r="C6" s="2">
@@ -658,7 +660,7 @@
       <c r="A7" s="3">
         <v>46083</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="9">
         <v>2</v>
       </c>
       <c r="C7" s="2">
@@ -677,7 +679,7 @@
       <c r="A8" s="3">
         <v>46084</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="9">
         <v>2</v>
       </c>
       <c r="C8" s="2">
@@ -696,7 +698,7 @@
       <c r="A9" s="3">
         <v>46086</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
       <c r="C9" s="2">
@@ -715,7 +717,7 @@
       <c r="A10" s="3">
         <v>46088</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="9">
         <v>2</v>
       </c>
       <c r="C10" s="2">
@@ -731,7 +733,7 @@
       <c r="A11" s="3">
         <v>46092</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="9">
         <v>2</v>
       </c>
       <c r="C11" s="2">
@@ -747,7 +749,7 @@
       <c r="A12" s="3">
         <v>46093</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="9">
         <v>2</v>
       </c>
       <c r="C12" s="2">
@@ -766,7 +768,7 @@
       <c r="A13" s="3">
         <v>46097</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>2</v>
       </c>
       <c r="C13" s="2">
@@ -782,7 +784,7 @@
       <c r="A14" s="3">
         <v>46098</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>2</v>
       </c>
       <c r="C14" s="2">
@@ -798,7 +800,7 @@
       <c r="A15" s="3">
         <v>45734</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <v>2</v>
       </c>
       <c r="C15" s="2">
@@ -814,15 +816,15 @@
       <c r="A16" s="3">
         <v>45735</v>
       </c>
-      <c r="B16" s="1">
-        <v>1</v>
+      <c r="B16" s="9">
+        <v>1.5</v>
       </c>
       <c r="C16" s="2">
         <v>30</v>
       </c>
       <c r="D16" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J16" s="2"/>
     </row>
@@ -830,15 +832,15 @@
       <c r="A17" s="3">
         <v>45739</v>
       </c>
-      <c r="B17" s="1">
-        <v>1</v>
+      <c r="B17" s="9">
+        <v>1.5</v>
       </c>
       <c r="C17" s="2">
         <v>30</v>
       </c>
       <c r="D17" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -846,40 +848,57 @@
       <c r="A18" s="3">
         <v>45740</v>
       </c>
-      <c r="B18" s="1">
-        <v>1</v>
+      <c r="B18" s="9">
+        <v>1.5</v>
       </c>
       <c r="C18" s="2">
         <v>30</v>
       </c>
       <c r="D18" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3">
+        <v>45741</v>
+      </c>
+      <c r="B19" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B20" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>33</v>
-      </c>
-      <c r="D19" s="2">
+        <v>36</v>
+      </c>
+      <c r="D20" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1000</v>
-      </c>
-      <c r="E19">
+        <v>1090</v>
+      </c>
+      <c r="E20">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ACDEA7-BC49-4A3F-B773-4B9687491833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30C76A6-AB61-41F7-8C81-3488C9539134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,22 +171,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -209,15 +209,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E20" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E19" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E22" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E21" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{F6272052-D21F-4D8F-847C-BBBD7A5BFBB5}" name="Taux (horaire)" dataDxfId="9" totalsRowDxfId="1">
+    <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F6272052-D21F-4D8F-847C-BBBD7A5BFBB5}" name="Taux (horaire)" dataDxfId="8" totalsRowDxfId="1">
       <calculatedColumnFormula>Tableau2[[#This Row],[Prix horaire]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0D374421-71FB-4B26-A655-B8932AB5024B}" name="Prix" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{0D374421-71FB-4B26-A655-B8932AB5024B}" name="Prix" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="0">
       <calculatedColumnFormula>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{AFE2A571-8D78-4F39-B21A-AD4ADB93030D}" name="Détails" totalsRowFunction="count"/>
@@ -230,11 +230,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9E2C1EA8-ABF8-4B8F-A346-A6735D728120}" name="Tableau2" displayName="Tableau2" ref="G1:J2" totalsRowShown="0">
   <autoFilter ref="G1:J2" xr:uid="{9E2C1EA8-ABF8-4B8F-A346-A6735D728120}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{66CCC7CF-8A36-43CE-820F-0890999AEE46}" name="Salaire" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{AD6BD5F4-3FC8-4450-A6E7-FDD7C0FEA506}" name="Horaire" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{66CCC7CF-8A36-43CE-820F-0890999AEE46}" name="Salaire" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{AD6BD5F4-3FC8-4450-A6E7-FDD7C0FEA506}" name="Horaire" dataDxfId="5">
       <calculatedColumnFormula>35*4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F29CA281-385D-4D4D-97E5-98E515379F73}" name="Heure / jour" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F29CA281-385D-4D4D-97E5-98E515379F73}" name="Heure / jour" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{6CCB0674-3E10-4292-8D20-2B8C7040EA90}" name="Prix horaire">
       <calculatedColumnFormula>Tableau2[[#This Row],[Salaire]]/Tableau2[[#This Row],[Horaire]]</calculatedColumnFormula>
     </tableColumn>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -798,7 +798,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>45734</v>
+        <v>46099</v>
       </c>
       <c r="B15" s="9">
         <v>2</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>45735</v>
+        <v>46100</v>
       </c>
       <c r="B16" s="9">
         <v>1.5</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>45739</v>
+        <v>46104</v>
       </c>
       <c r="B17" s="9">
         <v>1.5</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>45740</v>
+        <v>46105</v>
       </c>
       <c r="B18" s="9">
         <v>1.5</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>45741</v>
+        <v>46106</v>
       </c>
       <c r="B19" s="9">
         <v>1.5</v>
@@ -877,18 +877,50 @@
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B20" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>30</v>
+      </c>
+      <c r="D20" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B21" s="9">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B22" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>36</v>
-      </c>
-      <c r="D20" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="D22" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1090</v>
-      </c>
-      <c r="E20">
+        <v>1165</v>
+      </c>
+      <c r="E22">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30C76A6-AB61-41F7-8C81-3488C9539134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE038E0B-EC31-455F-A37E-6081BB1F7720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E22" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E21" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E24" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E23" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -721,11 +721,11 @@
         <v>2</v>
       </c>
       <c r="C10" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2">
         <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -909,18 +909,50 @@
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3">
+        <v>46110</v>
+      </c>
+      <c r="B22" s="9">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>30</v>
+      </c>
+      <c r="D22" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46111</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B24" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>38.5</v>
-      </c>
-      <c r="D22" s="2">
+        <v>42</v>
+      </c>
+      <c r="D24" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1165</v>
-      </c>
-      <c r="E22">
+        <v>1260</v>
+      </c>
+      <c r="E24">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE038E0B-EC31-455F-A37E-6081BB1F7720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4BCAC2-DCD1-4E9E-BD40-6EA95AA4CEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E24" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E23" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E25" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E24" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -941,18 +941,34 @@
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3">
+        <v>46121</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>30</v>
+      </c>
+      <c r="D24" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B25" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>42</v>
-      </c>
-      <c r="D24" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="D25" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1260</v>
-      </c>
-      <c r="E24">
+        <v>1305</v>
+      </c>
+      <c r="E25">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4BCAC2-DCD1-4E9E-BD40-6EA95AA4CEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9276072-1AD0-42BA-953F-0668834EFD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E25" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E24" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E26" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E25" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -957,18 +957,34 @@
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C25" s="2">
+        <v>30</v>
+      </c>
+      <c r="D25" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B26" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>43.5</v>
-      </c>
-      <c r="D25" s="2">
+        <v>45</v>
+      </c>
+      <c r="D26" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1305</v>
-      </c>
-      <c r="E25">
+        <v>1350</v>
+      </c>
+      <c r="E26">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9276072-1AD0-42BA-953F-0668834EFD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60663F1C-C093-4314-A4F0-C8302A028FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E26" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E25" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E28" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E27" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -973,18 +973,50 @@
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3">
+        <v>46131</v>
+      </c>
+      <c r="B26" s="9">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>30</v>
+      </c>
+      <c r="D26" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>46132</v>
+      </c>
+      <c r="B27" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C27" s="2">
+        <v>30</v>
+      </c>
+      <c r="D27" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B28" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>45</v>
-      </c>
-      <c r="D26" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="D28" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1350</v>
-      </c>
-      <c r="E26">
+        <v>1455</v>
+      </c>
+      <c r="E28">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60663F1C-C093-4314-A4F0-C8302A028FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F287AE-0B78-409C-8D95-10F08CADF03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24180" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E28" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E27" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E30" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E29" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -1005,18 +1005,50 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3">
+        <v>46137</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <v>30</v>
+      </c>
+      <c r="D28" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>46138</v>
+      </c>
+      <c r="B29" s="9">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>30</v>
+      </c>
+      <c r="D29" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>60</v>
+      </c>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B30" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>48.5</v>
-      </c>
-      <c r="D28" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="D30" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1455</v>
-      </c>
-      <c r="E28">
+        <v>1575</v>
+      </c>
+      <c r="E30">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F287AE-0B78-409C-8D95-10F08CADF03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D4D899-E146-4D2C-BB0A-3539192AC538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E30" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E29" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E32" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E31" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -1037,18 +1037,50 @@
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3">
+        <v>46139</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2">
+        <v>30</v>
+      </c>
+      <c r="D30" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>46140</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="C31" s="2">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>45</v>
+      </c>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B32" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>52.5</v>
-      </c>
-      <c r="D30" s="2">
+        <v>55</v>
+      </c>
+      <c r="D32" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1575</v>
-      </c>
-      <c r="E30">
+        <v>1650</v>
+      </c>
+      <c r="E32">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D4D899-E146-4D2C-BB0A-3539192AC538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5BE69B-0ED5-4BCE-BC54-06494F721678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E32" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E31" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E33" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E32" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -1069,18 +1069,34 @@
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="3">
+        <v>46145</v>
+      </c>
+      <c r="B32" s="9">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2">
+        <v>30</v>
+      </c>
+      <c r="D32" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>90</v>
+      </c>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B33" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>55</v>
-      </c>
-      <c r="D32" s="2">
+        <v>58</v>
+      </c>
+      <c r="D33" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1650</v>
-      </c>
-      <c r="E32">
+        <v>1740</v>
+      </c>
+      <c r="E33">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>

--- a/TimeTracker.xlsx
+++ b/TimeTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Works\KungFu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5BE69B-0ED5-4BCE-BC54-06494F721678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96CF098-440F-4665-B57E-0681CB8D7D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E33" totalsRowCount="1" headerRowDxfId="11">
-  <autoFilter ref="A1:E32" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}" name="Tableau1" displayName="Tableau1" ref="A1:E35" totalsRowCount="1" headerRowDxfId="11">
+  <autoFilter ref="A1:E34" xr:uid="{C07780F6-4EDD-4593-9309-66544A000426}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9CE1E16E-0A99-4229-9545-CEB505BEA2F7}" name="Jours" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3224133E-C10D-49BC-81D3-C06B33B14FB6}" name="Temps" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="2"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
@@ -1084,19 +1084,51 @@
       </c>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>46152</v>
+      </c>
+      <c r="B33" s="9">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2">
+        <v>30</v>
+      </c>
+      <c r="D33" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>90</v>
+      </c>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46153</v>
+      </c>
+      <c r="B34" s="9">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2">
+        <v>30</v>
+      </c>
+      <c r="D34" s="2">
+        <f>Tableau1[[#This Row],[Temps]]*Tableau1[[#This Row],[Taux (horaire)]]</f>
+        <v>30</v>
+      </c>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B35" s="1">
         <f>SUBTOTAL(109,Tableau1[Temps])</f>
-        <v>58</v>
-      </c>
-      <c r="D33" s="2">
+        <v>62</v>
+      </c>
+      <c r="D35" s="2">
         <f>SUBTOTAL(109,Tableau1[Prix])</f>
-        <v>1740</v>
-      </c>
-      <c r="E33">
+        <v>1860</v>
+      </c>
+      <c r="E35">
         <f>SUBTOTAL(103,Tableau1[Détails])</f>
         <v>9</v>
       </c>
